--- a/docs/downloads/DEX-Requirements-kommentiert.xlsx
+++ b/docs/downloads/DEX-Requirements-kommentiert.xlsx
@@ -2493,7 +2493,7 @@
       </c>
       <c r="H43" s="34" t="inlineStr">
         <is>
-          <t>Offenlegung: Eine Funktion nutzt ein Geheimnis, das nicht über KCM verwaltet wird — der Selbst-Check-in. Je Event liegt ein Zufallswert in der Event-Zeile, aus dem ein alle paar Sekunden wechselnder Code für den Aushang berechnet wird (HMAC-SHA-256). Es ist kein Schlüssel für Daten, sondern ein geteiltes Geheimnis für einen kurzlebigen Anzeigecode. Wirkung bei Kompromittierung: Ein Unbefugter könnte sich bei genau diesem Event einchecken. Er ist je Event verschieden und durch Neuerzeugen wechselbar. Bitte um Bewertung.</t>
+          <t>Offenlegung: Eine Funktion nutzt ein Geheimnis, das nicht über KCM verwaltet wird — der Selbst-Check-in. Je Event liegt ein Zufallswert in der Event-Zeile, aus dem ein alle paar Sekunden wechselnder Code für den Aushang berechnet wird (HMAC-SHA-256). Es ist kein Schlüssel für Daten, sondern ein geteiltes Geheimnis für einen kurzlebigen Anzeigecode. Wirkung bei Kompromittierung: Ein Unbefugter könnte sich bei genau diesem Event einchecken. Er ist je Event verschieden und durch Neuerzeugen wechselbar. WICHTIG zur Verbreitung: Die Funktion ist nicht opt-in. Seit v20.1 erzeugt der erste Klick auf die QR-Kachel den Wert und schaltet den Selbst-Check-in am Event scharf — die Kachel erscheint ab fünf Tagen vor Beginn beziehungsweise sobald QR-Codes versendet wurden. Die Zahl der Events mit einem solchen Geheimnis entspricht deshalb NICHT der Zahl der Events, die den Selbst-Check-in nutzen (laut Fachbereich in der Regel keines), sondern der Zahl der Events, bei denen jemand die Kachel einmal geöffnet hat. Empfehlung: Auto-Aktivierung entfernen (nur noch bewusstes Einschalten) und den Wert nach dem Event löschen. Danach ist die Abweichung auf die tatsächlich genutzten Events begrenzt und abzählbar.</t>
         </is>
       </c>
     </row>
@@ -2601,7 +2601,7 @@
       </c>
       <c r="H46" s="34" t="inlineStr">
         <is>
-          <t>Siehe GSC-03: Das Geheimnis für den Selbst-Check-in liegt als Feld in der Event-Liste und ist damit für Organizer dieses Events lesbar. Bewertung erbeten.</t>
+          <t>Siehe GSC-03: Das Geheimnis für den Selbst-Check-in liegt als Feld in der Event-Liste und ist damit für Organizer dieses Events lesbar. Zusätzlich relevant: Es entsteht heute automatisch beim ersten Öffnen der QR-Kachel, nicht durch eine bewusste Aktivierung. Bewertung erbeten; Empfehlung siehe GSC-03.</t>
         </is>
       </c>
     </row>

--- a/docs/downloads/DEX-Requirements-kommentiert.xlsx
+++ b/docs/downloads/DEX-Requirements-kommentiert.xlsx
@@ -154,7 +154,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FDF0DA"/>
+        <fgColor rgb="00FBE3E0"/>
       </patternFill>
     </fill>
     <fill>
@@ -169,12 +169,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FBE3E0"/>
+        <fgColor rgb="00EFEFEC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00EFEFEC"/>
+        <fgColor rgb="00FDF0DA"/>
       </patternFill>
     </fill>
   </fills>
@@ -282,13 +282,13 @@
     <xf numFmtId="0" fontId="13" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -861,7 +861,7 @@
         </is>
       </c>
       <c r="C9" s="24" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="10">
@@ -906,7 +906,7 @@
         </is>
       </c>
       <c r="C12" s="24" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="13">
@@ -921,7 +921,7 @@
         </is>
       </c>
       <c r="C13" s="24" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="14">
@@ -1100,24 +1100,24 @@
       <c r="D6" s="34" t="inlineStr">
         <is>
           <t>NOTE: The implementation of this security requirement must be verified validated by the SSDLC assessor.
-Architektur, Kapitel 7 „Die sieben Flows“ — Auflistung der Flows und ihrer Identität.
+Architektur, Kapitel 7 „Die sieben Flows“; Auskunft des Betriebs vom 2026-08-17.
 Systemarchitektur, Kapitel „Die sieben Flows“ (docs/architektur.html#k7)</t>
         </is>
       </c>
       <c r="E6" s="34" t="n"/>
       <c r="F6" s="35" t="inlineStr">
         <is>
-          <t>Offen</t>
+          <t>Zur Bewertung</t>
         </is>
       </c>
       <c r="G6" s="34" t="inlineStr">
         <is>
-          <t>DEX bringt keine eigenen privilegierten Konten mit. Im Umfang liegen genau zwei: die Websitesammlungs-Administratoren der SharePoint-Site (tenantverwaltet) und die Verbindungs-Identität der sieben Power-Automate-Flows, die auf den Event-Subsites Vollzugriff braucht.</t>
+          <t>DEX bringt keine eigenen privilegierten Konten mit. Im Umfang liegen zwei: die Websitesammlungs-Administratoren der SharePoint-Site (tenantverwaltet) und die Verbindungs-Identität der sieben Power-Automate-Flows, die auf den Event-Subsites Vollzugriff braucht.</t>
         </is>
       </c>
       <c r="H6" s="34" t="inlineStr">
         <is>
-          <t>Zu bestätigen: Läuft die Verbindungs-Identität der Flows unter einem Dienstkonto, das im PAMS hinterlegt ist? Diese Bestätigung kann nur der Betreiber der Flows geben.</t>
+          <t>Befund mit bekanntem Abhilfeplan: Die Flow-Verbindungen laufen derzeit unter einem PERSÖNLICHEN Benutzerkonto, nicht unter einem Dienstkonto. Damit ist kein Vaulting im PAMS möglich — ein persönliches Konto gehört dort nicht hinein. Zwei Wirkungen: Die Anforderung ist nicht erfüllt, und der Betrieb der Plattform hängt an einer Person; scheidet sie aus, brechen alle Mails und Kalendereinträge ab. Geplant ist die Umstellung auf einen Service Principal. Damit wäre die Anforderung erfüllbar und GAC-02 sowie GAC-15 gleich mit. Bitte Zieltermin festhalten.</t>
         </is>
       </c>
     </row>
@@ -1140,14 +1140,14 @@
       <c r="D7" s="34" t="inlineStr">
         <is>
           <t>NOTE: The implementation of this security requirement must be verified validated by the SSDLC assessor.
-Architektur, Kapitel 7.
+Architektur, Kapitel 7; Auskunft des Betriebs vom 2026-08-17.
 Systemarchitektur, Kapitel „Die sieben Flows“ (docs/architektur.html#k7)</t>
         </is>
       </c>
       <c r="E7" s="34" t="n"/>
       <c r="F7" s="35" t="inlineStr">
         <is>
-          <t>Offen</t>
+          <t>Zur Bewertung</t>
         </is>
       </c>
       <c r="G7" s="34" t="inlineStr">
@@ -1157,7 +1157,7 @@
       </c>
       <c r="H7" s="34" t="inlineStr">
         <is>
-          <t>Zu bestätigen: aktuelle Eigentümer- und Freigabeliste der sieben Flow-Verbindungen.</t>
+          <t>Derzeit ist die Verbindungs-Identität ein persönliches Konto (siehe GAC-01). Formal ist die Anforderung damit erfüllt — die Zugangsdaten liegen ausschliesslich bei ihrem Eigentümer —, aber aus dem falschen Grund: Es gibt keinen autorisierten Vertreter, weil es keine Delegation gibt. Mit dem geplanten Service Principal wird daraus eine bewusst verwaltete Berechtigung mit benennbaren Verantwortlichen.</t>
         </is>
       </c>
     </row>
@@ -1415,7 +1415,7 @@
       <c r="H14" s="34" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="40" t="inlineStr">
+      <c r="A15" s="33" t="inlineStr">
         <is>
           <t>GAC-14</t>
         </is>
@@ -1437,7 +1437,7 @@
         </is>
       </c>
       <c r="E15" s="34" t="n"/>
-      <c r="F15" s="41" t="inlineStr">
+      <c r="F15" s="35" t="inlineStr">
         <is>
           <t>Zur Bewertung</t>
         </is>
@@ -1467,24 +1467,24 @@
       <c r="C16" s="34" t="n"/>
       <c r="D16" s="34" t="inlineStr">
         <is>
-          <t>Architektur, Kapitel 7.
+          <t>Architektur, Kapitel 7; Auskunft des Betriebs vom 2026-08-17.
 Systemarchitektur, Kapitel „Die sieben Flows“ (docs/architektur.html#k7)</t>
         </is>
       </c>
       <c r="E16" s="34" t="n"/>
       <c r="F16" s="35" t="inlineStr">
         <is>
-          <t>Offen</t>
+          <t>Zur Bewertung</t>
         </is>
       </c>
       <c r="G16" s="34" t="inlineStr">
         <is>
-          <t>Die Verbindungs-Identität der Flows ist ein nicht-menschliches Konto.</t>
+          <t>Die Anforderung greift erst, wenn es ein nicht-menschliches Konto gibt.</t>
         </is>
       </c>
       <c r="H16" s="34" t="inlineStr">
         <is>
-          <t>Zu bestätigen durch den Betrieb: Interaktive Anmeldung für dieses Konto ist per Conditional Access unterbunden.</t>
+          <t>Heute nicht anwendbar, weil die Flows unter einem persönlichen Konto laufen (GAC-01) — und dem kann die interaktive Anmeldung nicht entzogen werden, es ist ja ein Mensch. Mit der Umstellung auf einen Service Principal löst sich die Anforderung von selbst: Ein Service Principal hat gar keine interaktive Anmeldung. Der Punkt ist also nicht separat zu bearbeiten, sondern erledigt sich mit GAC-01.</t>
         </is>
       </c>
     </row>
@@ -1606,7 +1606,7 @@
       <c r="H19" s="34" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="40" t="inlineStr">
+      <c r="A20" s="33" t="inlineStr">
         <is>
           <t>GAU-03</t>
         </is>
@@ -1628,7 +1628,7 @@
         </is>
       </c>
       <c r="E20" s="34" t="n"/>
-      <c r="F20" s="41" t="inlineStr">
+      <c r="F20" s="35" t="inlineStr">
         <is>
           <t>Zur Bewertung</t>
         </is>
@@ -1681,7 +1681,7 @@
       <c r="H21" s="34" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="40" t="inlineStr">
+      <c r="A22" s="33" t="inlineStr">
         <is>
           <t>GAU-05</t>
         </is>
@@ -1703,7 +1703,7 @@
         </is>
       </c>
       <c r="E22" s="34" t="n"/>
-      <c r="F22" s="41" t="inlineStr">
+      <c r="F22" s="35" t="inlineStr">
         <is>
           <t>Zur Bewertung</t>
         </is>
@@ -1720,7 +1720,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="42" t="inlineStr">
+      <c r="A23" s="40" t="inlineStr">
         <is>
           <t>GAU-07</t>
         </is>
@@ -1742,7 +1742,7 @@
         </is>
       </c>
       <c r="E23" s="34" t="n"/>
-      <c r="F23" s="43" t="inlineStr">
+      <c r="F23" s="41" t="inlineStr">
         <is>
           <t>Nicht anwendbar</t>
         </is>
@@ -1907,7 +1907,7 @@
       <c r="H27" s="34" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="33" t="inlineStr">
+      <c r="A28" s="38" t="inlineStr">
         <is>
           <t>GCM-07</t>
         </is>
@@ -1924,141 +1924,141 @@
       </c>
       <c r="D28" s="34" t="inlineStr">
         <is>
-          <t>Architektur, Kapitel 15.
+          <t>Architektur, Kapitel 15 „Deployment und Rollback“; Auskunft des Betriebs vom 2026-08-17. Nachweis: Power Platform zeigt zwei Umgebungen — GER-DTech-CDE-PowerTeam (produktiv) und GER-DTech-CDE-PowerTeam-DEV (Entwicklung); Screenshot vom 2026-08-17.
 Systemarchitektur, Kapitel „Deployment und Rollback“ (docs/architektur.html#k15)</t>
         </is>
       </c>
       <c r="E28" s="34" t="n"/>
-      <c r="F28" s="35" t="inlineStr">
+      <c r="F28" s="39" t="inlineStr">
+        <is>
+          <t>DEX</t>
+        </is>
+      </c>
+      <c r="G28" s="34" t="inlineStr">
+        <is>
+          <t>Für die Automatisierung gibt es zwei kategorisierte Umgebungen: Die Flows werden in einer DEV-Umgebung entwickelt und laufen produktiv in einer PROD-Umgebung von Power Platform. Die Anwendung selbst — das SPFx-Paket — liegt auf der Produktiv-Site; innerhalb der Anwendung sind Demo-Modus und Entwurfs-Events fachliche Zustände, keine Umgebungen.</t>
+        </is>
+      </c>
+      <c r="H28" s="34" t="inlineStr">
+        <is>
+          <t>Für die Anwendungsseite gibt es keine getrennte Nicht-Produktivumgebung (eigene Site Collection, eigener App-Katalog). Zu entscheiden, ob das gefordert ist; der Aufwand ist überschaubar, weil die Anwendung ihre Listen selbst anlegt.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="38" t="inlineStr">
+        <is>
+          <t>GCM-08</t>
+        </is>
+      </c>
+      <c r="B29" s="34" t="inlineStr">
+        <is>
+          <t>Ensure production and non-production environments are physically separated. Where physical separation cannot be achieved, logical separation of resources and configurations must be applied.</t>
+        </is>
+      </c>
+      <c r="C29" s="34" t="inlineStr">
+        <is>
+          <t>All environments intended for a specific solution must be documented in the solution design.</t>
+        </is>
+      </c>
+      <c r="D29" s="34" t="inlineStr">
+        <is>
+          <t>Architektur, Kapitel 15; Auskunft des Betriebs vom 2026-08-17. Nachweis: Power Platform zeigt zwei Umgebungen — GER-DTech-CDE-PowerTeam (produktiv) und GER-DTech-CDE-PowerTeam-DEV (Entwicklung); Screenshot vom 2026-08-17.
+Systemarchitektur, Kapitel „Deployment und Rollback“ (docs/architektur.html#k15)</t>
+        </is>
+      </c>
+      <c r="E29" s="34" t="n"/>
+      <c r="F29" s="39" t="inlineStr">
+        <is>
+          <t>DEX</t>
+        </is>
+      </c>
+      <c r="G29" s="34" t="inlineStr">
+        <is>
+          <t>Die Trennung ist für die Flows logisch umgesetzt: DEV und PROD sind eigene Power-Platform-Umgebungen mit eigenen Verbindungen und eigenen Zugriffsrechten. Eine physische Trennung ist bei einem Cloud-Dienst nicht darstellbar und auch nicht gefordert.</t>
+        </is>
+      </c>
+      <c r="H29" s="34" t="inlineStr">
+        <is>
+          <t>Zu bestätigen: Greifen die DEV-Flows auf eine eigene SharePoint-Site zu oder auf die Produktiv-Site? Zeigen sie auf die Produktivdaten, ist die Trennung nur nominell — siehe GCM-10.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="42" t="inlineStr">
+        <is>
+          <t>GCM-09</t>
+        </is>
+      </c>
+      <c r="B30" s="34" t="inlineStr">
+        <is>
+          <t>Non-production environments must not allow end user access, except controlled access for user acceptance testing purposes.</t>
+        </is>
+      </c>
+      <c r="C30" s="34" t="inlineStr">
+        <is>
+          <t>All environments intended for a specific solution must be documented in the solution design and in the authorisation concept. Developers are also endusers and must have access to test environments, it must be limited to the need to know.</t>
+        </is>
+      </c>
+      <c r="D30" s="34" t="inlineStr">
+        <is>
+          <t>Architektur, Kapitel 15; Auskunft des Betriebs vom 2026-08-17. Nachweis: Power Platform zeigt zwei Umgebungen — GER-DTech-CDE-PowerTeam (produktiv) und GER-DTech-CDE-PowerTeam-DEV (Entwicklung); Screenshot vom 2026-08-17.
+Systemarchitektur, Kapitel „Deployment und Rollback“ (docs/architektur.html#k15)</t>
+        </is>
+      </c>
+      <c r="E30" s="34" t="n"/>
+      <c r="F30" s="43" t="inlineStr">
         <is>
           <t>Offen</t>
         </is>
       </c>
-      <c r="G28" s="34" t="inlineStr">
-        <is>
-          <t>DEX wird heute in einer Umgebung betrieben: der Produktiv-Site der Plattform. Innerhalb der Anwendung gibt es einen Demo-Modus mit synthetischen Daten und Entwurfs-Events, die für Teilnehmer unsichtbar sind — beides sind fachliche Zustände, keine getrennten Umgebungen.</t>
-        </is>
-      </c>
-      <c r="H28" s="34" t="inlineStr">
-        <is>
-          <t>Offen: Eine dedizierte Nicht-Produktivumgebung (eigene Site Collection, eigener App-Katalog, eigene Flows) existiert derzeit nicht. Ob sie gefordert ist, ist zu entscheiden; der Aufwand ist überschaubar, weil die Anwendung ihre Listen selbst anlegt.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="33" t="inlineStr">
-        <is>
-          <t>GCM-08</t>
-        </is>
-      </c>
-      <c r="B29" s="34" t="inlineStr">
-        <is>
-          <t>Ensure production and non-production environments are physically separated. Where physical separation cannot be achieved, logical separation of resources and configurations must be applied.</t>
-        </is>
-      </c>
-      <c r="C29" s="34" t="inlineStr">
-        <is>
-          <t>All environments intended for a specific solution must be documented in the solution design.</t>
-        </is>
-      </c>
-      <c r="D29" s="34" t="inlineStr">
-        <is>
-          <t>Architektur, Kapitel 15.
+      <c r="G30" s="34" t="inlineStr">
+        <is>
+          <t>Die DEV-Umgebung der Flows ist keine Umgebung für Endnutzer — sie enthält keine Anwendungsoberfläche, sondern nur Flow-Entwürfe. Endnutzer erreichen sie nicht, weil es dort nichts zu erreichen gibt.</t>
+        </is>
+      </c>
+      <c r="H30" s="34" t="inlineStr">
+        <is>
+          <t>Zu bestätigen: Wer hat Zugriff auf die DEV-Umgebung? Für die Anforderung genügt die Aussage, dass es der Entwicklungskreis ist und keine Endnutzer.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="42" t="inlineStr">
+        <is>
+          <t>GCM-10</t>
+        </is>
+      </c>
+      <c r="B31" s="34" t="inlineStr">
+        <is>
+          <t>Non-production accounts must not have access to production data or production systems.</t>
+        </is>
+      </c>
+      <c r="C31" s="34" t="inlineStr">
+        <is>
+          <t>All environments intended for a specific solution must be documented in the solution design and in the authorisation concept</t>
+        </is>
+      </c>
+      <c r="D31" s="34" t="inlineStr">
+        <is>
+          <t>Architektur, Kapitel 15 und 17; Auskunft des Betriebs vom 2026-08-17.
 Systemarchitektur, Kapitel „Deployment und Rollback“ (docs/architektur.html#k15)</t>
         </is>
       </c>
-      <c r="E29" s="34" t="n"/>
-      <c r="F29" s="35" t="inlineStr">
+      <c r="E31" s="34" t="n"/>
+      <c r="F31" s="43" t="inlineStr">
         <is>
           <t>Offen</t>
         </is>
       </c>
-      <c r="G29" s="34" t="inlineStr">
-        <is>
-          <t>Siehe GCM-07 — ohne zweite Umgebung ist eine Trennung nicht darstellbar.</t>
-        </is>
-      </c>
-      <c r="H29" s="34" t="inlineStr">
-        <is>
-          <t>Entscheidung zu GCM-07 abwarten.</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="33" t="inlineStr">
-        <is>
-          <t>GCM-09</t>
-        </is>
-      </c>
-      <c r="B30" s="34" t="inlineStr">
-        <is>
-          <t>Non-production environments must not allow end user access, except controlled access for user acceptance testing purposes.</t>
-        </is>
-      </c>
-      <c r="C30" s="34" t="inlineStr">
-        <is>
-          <t>All environments intended for a specific solution must be documented in the solution design and in the authorisation concept. Developers are also endusers and must have access to test environments, it must be limited to the need to know.</t>
-        </is>
-      </c>
-      <c r="D30" s="34" t="inlineStr">
-        <is>
-          <t>Architektur, Kapitel 15.
-Systemarchitektur, Kapitel „Deployment und Rollback“ (docs/architektur.html#k15)</t>
-        </is>
-      </c>
-      <c r="E30" s="34" t="n"/>
-      <c r="F30" s="35" t="inlineStr">
-        <is>
-          <t>Offen</t>
-        </is>
-      </c>
-      <c r="G30" s="34" t="inlineStr">
-        <is>
-          <t>Siehe GCM-07.</t>
-        </is>
-      </c>
-      <c r="H30" s="34" t="inlineStr">
-        <is>
-          <t>Entscheidung zu GCM-07 abwarten.</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="33" t="inlineStr">
-        <is>
-          <t>GCM-10</t>
-        </is>
-      </c>
-      <c r="B31" s="34" t="inlineStr">
-        <is>
-          <t>Non-production accounts must not have access to production data or production systems.</t>
-        </is>
-      </c>
-      <c r="C31" s="34" t="inlineStr">
-        <is>
-          <t>All environments intended for a specific solution must be documented in the solution design and in the authorisation concept</t>
-        </is>
-      </c>
-      <c r="D31" s="34" t="inlineStr">
-        <is>
-          <t>Architektur, Kapitel 15 und 17.
-Systemarchitektur, Kapitel „Deployment und Rollback“ (docs/architektur.html#k15)</t>
-        </is>
-      </c>
-      <c r="E31" s="34" t="n"/>
-      <c r="F31" s="35" t="inlineStr">
-        <is>
-          <t>Offen</t>
-        </is>
-      </c>
       <c r="G31" s="34" t="inlineStr">
         <is>
-          <t>Siehe GCM-07. Innerhalb der Produktivumgebung gilt: Der Demo-Modus liest keine Produktionsdaten, sondern erzeugt seine Datensätze zur Laufzeit.</t>
+          <t>Auf Anwendungsseite gilt: Der Demo-Modus liest keine Produktionsdaten, sondern erzeugt seine Datensätze zur Laufzeit.</t>
         </is>
       </c>
       <c r="H31" s="34" t="inlineStr">
         <is>
-          <t>Entscheidung zu GCM-07 abwarten.</t>
+          <t>Die entscheidende offene Frage dieses Blocks: Verbinden sich die Flows der DEV-Umgebung mit der Produktiv-SharePoint-Site? Wenn ja, greifen Nicht-Produktivkonten auf Produktionsdaten zu — und dann sind GCM-08, GCM-10 und GCM-16 betroffen, unabhängig davon, dass die Umgebungen getrennt sind. Wenn nein, ist der Block sauber. Diese eine Antwort entscheidet über drei Anforderungen.</t>
         </is>
       </c>
     </row>
@@ -2080,7 +2080,7 @@
       </c>
       <c r="D32" s="34" t="inlineStr">
         <is>
-          <t>Architektur, Kapitel 15; Release-Ablauf in den Arbeitsanweisungen des Repositories.
+          <t>Architektur, Kapitel 15; Release-Ablauf in den Arbeitsanweisungen des Repositories; Auskunft des Betriebs vom 2026-08-17. Nachweis: Power Platform zeigt zwei Umgebungen — GER-DTech-CDE-PowerTeam (produktiv) und GER-DTech-CDE-PowerTeam-DEV (Entwicklung); Screenshot vom 2026-08-17.
 Systemarchitektur, Kapitel „Deployment und Rollback“ (docs/architektur.html#k15)</t>
         </is>
       </c>
@@ -2092,10 +2092,14 @@
       </c>
       <c r="G32" s="34" t="inlineStr">
         <is>
-          <t>Der Weg in die Produktion ist festgelegt und dokumentiert: Versionsnummer an drei Stellen setzen, Release Notes schreiben, Typprüfung, sauberer Build, Paket ablegen, Bereitstellung über den App-Katalog. Jeder Schritt ist im Repository beschrieben und im Versionsverlauf nachvollziehbar.</t>
-        </is>
-      </c>
-      <c r="H32" s="34" t="inlineStr"/>
+          <t>Es gibt zwei getrennte Wege, beide festgelegt. Anwendung: Versionsnummer setzen, Release Notes schreiben, Typprüfung, sauberer Build, Paket ablegen, Bereitstellung über den App-Katalog — jeder Schritt im Repository beschrieben und im Versionsverlauf nachvollziehbar. Flows: Entwicklung in der DEV-Umgebung, produktiver Betrieb in der PROD-Umgebung von Power Platform.</t>
+        </is>
+      </c>
+      <c r="H32" s="34" t="inlineStr">
+        <is>
+          <t>Zu ergänzen: Wie kommt ein Flow von DEV nach PROD — als Solution-Export und -Import oder von Hand nachgebaut? Der Unterschied ist für GCM-04 wesentlich, weil nur der erste Weg einen nachvollziehbaren Rückfall erlaubt.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="38" t="inlineStr">
@@ -2137,7 +2141,7 @@
       <c r="H33" s="34" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="42" t="inlineStr">
+      <c r="A34" s="40" t="inlineStr">
         <is>
           <t>GCM-18</t>
         </is>
@@ -2160,7 +2164,7 @@
         </is>
       </c>
       <c r="E34" s="34" t="n"/>
-      <c r="F34" s="43" t="inlineStr">
+      <c r="F34" s="41" t="inlineStr">
         <is>
           <t>Nicht anwendbar</t>
         </is>
@@ -2177,7 +2181,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="42" t="inlineStr">
+      <c r="A35" s="40" t="inlineStr">
         <is>
           <t>GCM-22</t>
         </is>
@@ -2200,7 +2204,7 @@
         </is>
       </c>
       <c r="E35" s="34" t="n"/>
-      <c r="F35" s="43" t="inlineStr">
+      <c r="F35" s="41" t="inlineStr">
         <is>
           <t>Nicht anwendbar</t>
         </is>
@@ -2288,7 +2292,7 @@
       <c r="H37" s="34" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="42" t="inlineStr">
+      <c r="A38" s="40" t="inlineStr">
         <is>
           <t>GIA-02</t>
         </is>
@@ -2310,7 +2314,7 @@
         </is>
       </c>
       <c r="E38" s="34" t="n"/>
-      <c r="F38" s="43" t="inlineStr">
+      <c r="F38" s="41" t="inlineStr">
         <is>
           <t>Nicht anwendbar</t>
         </is>
@@ -2422,7 +2426,7 @@
       <c r="H41" s="34" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="42" t="inlineStr">
+      <c r="A42" s="40" t="inlineStr">
         <is>
           <t>GSC-01</t>
         </is>
@@ -2444,7 +2448,7 @@
         </is>
       </c>
       <c r="E42" s="34" t="n"/>
-      <c r="F42" s="43" t="inlineStr">
+      <c r="F42" s="41" t="inlineStr">
         <is>
           <t>Nicht anwendbar</t>
         </is>
@@ -2457,7 +2461,7 @@
       <c r="H42" s="34" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="40" t="inlineStr">
+      <c r="A43" s="33" t="inlineStr">
         <is>
           <t>GSC-03</t>
         </is>
@@ -2481,7 +2485,7 @@
         </is>
       </c>
       <c r="E43" s="34" t="n"/>
-      <c r="F43" s="41" t="inlineStr">
+      <c r="F43" s="35" t="inlineStr">
         <is>
           <t>Zur Bewertung</t>
         </is>
@@ -2566,7 +2570,7 @@
       <c r="H45" s="34" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="A46" s="40" t="inlineStr">
+      <c r="A46" s="33" t="inlineStr">
         <is>
           <t>GSC-06</t>
         </is>
@@ -2589,7 +2593,7 @@
         </is>
       </c>
       <c r="E46" s="34" t="n"/>
-      <c r="F46" s="41" t="inlineStr">
+      <c r="F46" s="35" t="inlineStr">
         <is>
           <t>Zur Bewertung</t>
         </is>
@@ -2672,7 +2676,7 @@
       <c r="H48" s="34" t="inlineStr"/>
     </row>
     <row r="49">
-      <c r="A49" s="40" t="inlineStr">
+      <c r="A49" s="33" t="inlineStr">
         <is>
           <t>GSI-06</t>
         </is>
@@ -2698,7 +2702,7 @@
         </is>
       </c>
       <c r="E49" s="34" t="n"/>
-      <c r="F49" s="41" t="inlineStr">
+      <c r="F49" s="35" t="inlineStr">
         <is>
           <t>Zur Bewertung</t>
         </is>
@@ -2715,7 +2719,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="33" t="inlineStr">
+      <c r="A50" s="42" t="inlineStr">
         <is>
           <t>GSI-09</t>
         </is>
@@ -2733,7 +2737,7 @@
         </is>
       </c>
       <c r="E50" s="34" t="n"/>
-      <c r="F50" s="35" t="inlineStr">
+      <c r="F50" s="43" t="inlineStr">
         <is>
           <t>Offen</t>
         </is>
@@ -2750,7 +2754,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="33" t="inlineStr">
+      <c r="A51" s="42" t="inlineStr">
         <is>
           <t>GSA-04</t>
         </is>
@@ -2769,7 +2773,7 @@
         </is>
       </c>
       <c r="E51" s="34" t="n"/>
-      <c r="F51" s="35" t="inlineStr">
+      <c r="F51" s="43" t="inlineStr">
         <is>
           <t>Offen</t>
         </is>
@@ -2819,7 +2823,7 @@
       <c r="H52" s="34" t="inlineStr"/>
     </row>
     <row r="53">
-      <c r="A53" s="40" t="inlineStr">
+      <c r="A53" s="33" t="inlineStr">
         <is>
           <t>GSD-02</t>
         </is>
@@ -2837,7 +2841,7 @@
         </is>
       </c>
       <c r="E53" s="34" t="n"/>
-      <c r="F53" s="41" t="inlineStr">
+      <c r="F53" s="35" t="inlineStr">
         <is>
           <t>Zur Bewertung</t>
         </is>
@@ -2854,7 +2858,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="42" t="inlineStr">
+      <c r="A54" s="40" t="inlineStr">
         <is>
           <t>GWAF-01</t>
         </is>
@@ -2872,7 +2876,7 @@
         </is>
       </c>
       <c r="E54" s="34" t="n"/>
-      <c r="F54" s="43" t="inlineStr">
+      <c r="F54" s="41" t="inlineStr">
         <is>
           <t>Nicht anwendbar</t>
         </is>

--- a/docs/downloads/DEX-Requirements-kommentiert.xlsx
+++ b/docs/downloads/DEX-Requirements-kommentiert.xlsx
@@ -861,7 +861,7 @@
         </is>
       </c>
       <c r="C9" s="24" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
     </row>
     <row r="10">
@@ -906,7 +906,7 @@
         </is>
       </c>
       <c r="C12" s="24" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
@@ -921,7 +921,7 @@
         </is>
       </c>
       <c r="C13" s="24" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
     </row>
     <row r="14">
@@ -1907,7 +1907,7 @@
       <c r="H27" s="34" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="38" t="inlineStr">
+      <c r="A28" s="33" t="inlineStr">
         <is>
           <t>GCM-07</t>
         </is>
@@ -1924,29 +1924,29 @@
       </c>
       <c r="D28" s="34" t="inlineStr">
         <is>
-          <t>Architektur, Kapitel 15 „Deployment und Rollback“; Auskunft des Betriebs vom 2026-08-17. Nachweis: Power Platform zeigt zwei Umgebungen — GER-DTech-CDE-PowerTeam (produktiv) und GER-DTech-CDE-PowerTeam-DEV (Entwicklung); Screenshot vom 2026-08-17.
+          <t>Architektur, Kapitel 15 „Deployment und Rollback“ (Ist-Stand und Zielmodell); Auskunft des Betriebs vom 2026-08-17. Nachweis: Power Platform zeigt zwei Umgebungen — GER-DTech-CDE-PowerTeam (produktiv) und GER-DTech-CDE-PowerTeam-DEV (Entwicklung).
 Systemarchitektur, Kapitel „Deployment und Rollback“ (docs/architektur.html#k15)</t>
         </is>
       </c>
       <c r="E28" s="34" t="n"/>
-      <c r="F28" s="39" t="inlineStr">
-        <is>
-          <t>DEX</t>
+      <c r="F28" s="35" t="inlineStr">
+        <is>
+          <t>Zur Bewertung</t>
         </is>
       </c>
       <c r="G28" s="34" t="inlineStr">
         <is>
-          <t>Für die Automatisierung gibt es zwei kategorisierte Umgebungen: Die Flows werden in einer DEV-Umgebung entwickelt und laufen produktiv in einer PROD-Umgebung von Power Platform. Die Anwendung selbst — das SPFx-Paket — liegt auf der Produktiv-Site; innerhalb der Anwendung sind Demo-Modus und Entwurfs-Events fachliche Zustände, keine Umgebungen.</t>
+          <t>Es gibt zwei benannte Umgebungen für die Automatisierung, DEV und PROD. Die Kategorisierung beschreibt den Betrieb aber nicht: Die sieben Flows liegen vollständig in der DEV-Umgebung und laufen von dort produktiv gegen die Produktiv-Site. Sie sind fertig und werden nicht mehr weiterentwickelt — die DEV-Umgebung ist damit faktisch die Produktionsumgebung. Für die SPFx-Anwendung existiert gar keine zweite Umgebung; sie liegt allein auf der Produktiv-Site.</t>
         </is>
       </c>
       <c r="H28" s="34" t="inlineStr">
         <is>
-          <t>Für die Anwendungsseite gibt es keine getrennte Nicht-Produktivumgebung (eigene Site Collection, eigener App-Katalog). Zu entscheiden, ob das gefordert ist; der Aufwand ist überschaubar, weil die Anwendung ihre Listen selbst anlegt.</t>
+          <t>Abweichung, offen benannt: Kategorien sind vergeben, die produktive Last liegt aber in der als Entwicklung kategorisierten Umgebung. Damit ist die Anforderung nicht erfüllt. Zielmodell (vom Betrieb benannt): Flows in die PROD-Umgebung überführen, dort unter einem Service Principal betreiben, der DEV-Umgebung den Zugriff auf Produktivdaten entziehen und eine DEV-Umgebung für die SPFx-Anwendung aufbauen. Damit lösen sich GCM-07 bis GCM-11 und GCM-16 gemeinsam, ebenso GAC-01, GAC-02 und GAC-15. Bitte Zieltermin festhalten.</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="38" t="inlineStr">
+      <c r="A29" s="33" t="inlineStr">
         <is>
           <t>GCM-08</t>
         </is>
@@ -1963,29 +1963,29 @@
       </c>
       <c r="D29" s="34" t="inlineStr">
         <is>
-          <t>Architektur, Kapitel 15; Auskunft des Betriebs vom 2026-08-17. Nachweis: Power Platform zeigt zwei Umgebungen — GER-DTech-CDE-PowerTeam (produktiv) und GER-DTech-CDE-PowerTeam-DEV (Entwicklung); Screenshot vom 2026-08-17.
+          <t>Architektur, Kapitel 15 „Deployment und Rollback“ (Ist-Stand und Zielmodell); Auskunft des Betriebs vom 2026-08-17. Nachweis: Power Platform zeigt zwei Umgebungen — GER-DTech-CDE-PowerTeam (produktiv) und GER-DTech-CDE-PowerTeam-DEV (Entwicklung).
 Systemarchitektur, Kapitel „Deployment und Rollback“ (docs/architektur.html#k15)</t>
         </is>
       </c>
       <c r="E29" s="34" t="n"/>
-      <c r="F29" s="39" t="inlineStr">
-        <is>
-          <t>DEX</t>
+      <c r="F29" s="35" t="inlineStr">
+        <is>
+          <t>Zur Bewertung</t>
         </is>
       </c>
       <c r="G29" s="34" t="inlineStr">
         <is>
-          <t>Die Trennung ist für die Flows logisch umgesetzt: DEV und PROD sind eigene Power-Platform-Umgebungen mit eigenen Verbindungen und eigenen Zugriffsrechten. Eine physische Trennung ist bei einem Cloud-Dienst nicht darstellbar und auch nicht gefordert.</t>
+          <t>Die beiden Power-Platform-Umgebungen sind logisch getrennt und haben eigene Verbindungen und Zugriffsrechte.</t>
         </is>
       </c>
       <c r="H29" s="34" t="inlineStr">
         <is>
-          <t>Zu bestätigen: Greifen die DEV-Flows auf eine eigene SharePoint-Site zu oder auf die Produktiv-Site? Zeigen sie auf die Produktivdaten, ist die Trennung nur nominell — siehe GCM-10.</t>
+          <t>Abweichung: Die Trennung ist nominell, weil die Verbindungen der DEV-Umgebung auf die Produktiv-SharePoint-Site zeigen. Eine Trennung, die auf dieselben Daten greift, trennt nichts, was diese Anforderung schützen soll. Zielmodell (vom Betrieb benannt): Flows in die PROD-Umgebung überführen, dort unter einem Service Principal betreiben, der DEV-Umgebung den Zugriff auf Produktivdaten entziehen und eine DEV-Umgebung für die SPFx-Anwendung aufbauen. Damit lösen sich GCM-07 bis GCM-11 und GCM-16 gemeinsam, ebenso GAC-01, GAC-02 und GAC-15. Bitte Zieltermin festhalten.</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="42" t="inlineStr">
+      <c r="A30" s="33" t="inlineStr">
         <is>
           <t>GCM-09</t>
         </is>
@@ -2002,29 +2002,29 @@
       </c>
       <c r="D30" s="34" t="inlineStr">
         <is>
-          <t>Architektur, Kapitel 15; Auskunft des Betriebs vom 2026-08-17. Nachweis: Power Platform zeigt zwei Umgebungen — GER-DTech-CDE-PowerTeam (produktiv) und GER-DTech-CDE-PowerTeam-DEV (Entwicklung); Screenshot vom 2026-08-17.
+          <t>Architektur, Kapitel 15 „Deployment und Rollback“ (Ist-Stand und Zielmodell); Auskunft des Betriebs vom 2026-08-17. Nachweis: Power Platform zeigt zwei Umgebungen — GER-DTech-CDE-PowerTeam (produktiv) und GER-DTech-CDE-PowerTeam-DEV (Entwicklung).
 Systemarchitektur, Kapitel „Deployment und Rollback“ (docs/architektur.html#k15)</t>
         </is>
       </c>
       <c r="E30" s="34" t="n"/>
-      <c r="F30" s="43" t="inlineStr">
-        <is>
-          <t>Offen</t>
+      <c r="F30" s="35" t="inlineStr">
+        <is>
+          <t>Zur Bewertung</t>
         </is>
       </c>
       <c r="G30" s="34" t="inlineStr">
         <is>
-          <t>Die DEV-Umgebung der Flows ist keine Umgebung für Endnutzer — sie enthält keine Anwendungsoberfläche, sondern nur Flow-Entwürfe. Endnutzer erreichen sie nicht, weil es dort nichts zu erreichen gibt.</t>
+          <t>Die DEV-Umgebung hat keine Anwendungsoberfläche — Endnutzer melden sich dort nicht an, es gibt nichts zu bedienen. Zugriff hat der Entwicklungskreis.</t>
         </is>
       </c>
       <c r="H30" s="34" t="inlineStr">
         <is>
-          <t>Zu bestätigen: Wer hat Zugriff auf die DEV-Umgebung? Für die Anforderung genügt die Aussage, dass es der Entwicklungskreis ist und keine Endnutzer.</t>
+          <t>Abweichung im Sinn der Anforderung: Endnutzer greifen zwar nicht selbst zu, werden aber aus dieser Umgebung bedient — jede Bestätigungsmail und jeder Kalendereintrag entsteht dort. Der Schutzzweck (keine produktive Nutzung aus einer Nicht-Produktivumgebung) ist damit nicht erfüllt. Zielmodell (vom Betrieb benannt): Flows in die PROD-Umgebung überführen, dort unter einem Service Principal betreiben, der DEV-Umgebung den Zugriff auf Produktivdaten entziehen und eine DEV-Umgebung für die SPFx-Anwendung aufbauen. Damit lösen sich GCM-07 bis GCM-11 und GCM-16 gemeinsam, ebenso GAC-01, GAC-02 und GAC-15. Bitte Zieltermin festhalten.</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="42" t="inlineStr">
+      <c r="A31" s="33" t="inlineStr">
         <is>
           <t>GCM-10</t>
         </is>
@@ -2041,14 +2041,14 @@
       </c>
       <c r="D31" s="34" t="inlineStr">
         <is>
-          <t>Architektur, Kapitel 15 und 17; Auskunft des Betriebs vom 2026-08-17.
+          <t>Architektur, Kapitel 15 „Deployment und Rollback“ (Ist-Stand und Zielmodell); Auskunft des Betriebs vom 2026-08-17. Nachweis: Power Platform zeigt zwei Umgebungen — GER-DTech-CDE-PowerTeam (produktiv) und GER-DTech-CDE-PowerTeam-DEV (Entwicklung).
 Systemarchitektur, Kapitel „Deployment und Rollback“ (docs/architektur.html#k15)</t>
         </is>
       </c>
       <c r="E31" s="34" t="n"/>
-      <c r="F31" s="43" t="inlineStr">
-        <is>
-          <t>Offen</t>
+      <c r="F31" s="35" t="inlineStr">
+        <is>
+          <t>Zur Bewertung</t>
         </is>
       </c>
       <c r="G31" s="34" t="inlineStr">
@@ -2058,12 +2058,12 @@
       </c>
       <c r="H31" s="34" t="inlineStr">
         <is>
-          <t>Die entscheidende offene Frage dieses Blocks: Verbinden sich die Flows der DEV-Umgebung mit der Produktiv-SharePoint-Site? Wenn ja, greifen Nicht-Produktivkonten auf Produktionsdaten zu — und dann sind GCM-08, GCM-10 und GCM-16 betroffen, unabhängig davon, dass die Umgebungen getrennt sind. Wenn nein, ist der Block sauber. Diese eine Antwort entscheidet über drei Anforderungen.</t>
+          <t>Abweichung, klar benannt: Die Verbindungen der als Nicht-Produktion kategorisierten DEV-Umgebung greifen auf die Produktiv-Site zu und damit auf personenbezogene Teilnehmerdaten. Die Anforderung ist nicht erfüllt. Der Entzug dieses Zugriffs ist ausdrücklich Teil des Zielmodells. Zielmodell (vom Betrieb benannt): Flows in die PROD-Umgebung überführen, dort unter einem Service Principal betreiben, der DEV-Umgebung den Zugriff auf Produktivdaten entziehen und eine DEV-Umgebung für die SPFx-Anwendung aufbauen. Damit lösen sich GCM-07 bis GCM-11 und GCM-16 gemeinsam, ebenso GAC-01, GAC-02 und GAC-15. Bitte Zieltermin festhalten.</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="38" t="inlineStr">
+      <c r="A32" s="33" t="inlineStr">
         <is>
           <t>GCM-11</t>
         </is>
@@ -2080,29 +2080,29 @@
       </c>
       <c r="D32" s="34" t="inlineStr">
         <is>
-          <t>Architektur, Kapitel 15; Release-Ablauf in den Arbeitsanweisungen des Repositories; Auskunft des Betriebs vom 2026-08-17. Nachweis: Power Platform zeigt zwei Umgebungen — GER-DTech-CDE-PowerTeam (produktiv) und GER-DTech-CDE-PowerTeam-DEV (Entwicklung); Screenshot vom 2026-08-17.
+          <t>Architektur, Kapitel 15 „Deployment und Rollback“ (Ist-Stand und Zielmodell); Auskunft des Betriebs vom 2026-08-17. Nachweis: Power Platform zeigt zwei Umgebungen — GER-DTech-CDE-PowerTeam (produktiv) und GER-DTech-CDE-PowerTeam-DEV (Entwicklung).
 Systemarchitektur, Kapitel „Deployment und Rollback“ (docs/architektur.html#k15)</t>
         </is>
       </c>
       <c r="E32" s="34" t="n"/>
-      <c r="F32" s="39" t="inlineStr">
-        <is>
-          <t>DEX</t>
+      <c r="F32" s="35" t="inlineStr">
+        <is>
+          <t>Zur Bewertung</t>
         </is>
       </c>
       <c r="G32" s="34" t="inlineStr">
         <is>
-          <t>Es gibt zwei getrennte Wege, beide festgelegt. Anwendung: Versionsnummer setzen, Release Notes schreiben, Typprüfung, sauberer Build, Paket ablegen, Bereitstellung über den App-Katalog — jeder Schritt im Repository beschrieben und im Versionsverlauf nachvollziehbar. Flows: Entwicklung in der DEV-Umgebung, produktiver Betrieb in der PROD-Umgebung von Power Platform.</t>
+          <t>Für die Anwendung ist der Weg in die Produktion festgelegt und dokumentiert: Version setzen, Release Notes, Typprüfung, sauberer Build, Paket ablegen, Bereitstellung über den App-Katalog — nachvollziehbar im Versionsverlauf.</t>
         </is>
       </c>
       <c r="H32" s="34" t="inlineStr">
         <is>
-          <t>Zu ergänzen: Wie kommt ein Flow von DEV nach PROD — als Solution-Export und -Import oder von Hand nachgebaut? Der Unterschied ist für GCM-04 wesentlich, weil nur der erste Weg einen nachvollziehbaren Rückfall erlaubt.</t>
+          <t>Für die Flows gibt es heute keinen solchen Weg, weil sie die DEV-Umgebung nie verlassen haben. Die Anforderung greift erst mit dem Zielmodell; dann ist festzulegen, ob die Überführung als Solution-Export und -Import erfolgt. Nur dieser Weg erlaubt einen nachvollziehbaren Rückfall (siehe GCM-04). Zielmodell (vom Betrieb benannt): Flows in die PROD-Umgebung überführen, dort unter einem Service Principal betreiben, der DEV-Umgebung den Zugriff auf Produktivdaten entziehen und eine DEV-Umgebung für die SPFx-Anwendung aufbauen. Damit lösen sich GCM-07 bis GCM-11 und GCM-16 gemeinsam, ebenso GAC-01, GAC-02 und GAC-15. Bitte Zieltermin festhalten.</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="38" t="inlineStr">
+      <c r="A33" s="33" t="inlineStr">
         <is>
           <t>GCM-16</t>
         </is>
@@ -2123,22 +2123,26 @@
       </c>
       <c r="D33" s="34" t="inlineStr">
         <is>
-          <t>Architektur, Kapitel 17; Funktion buildDemoRegistrations im EventContext.
-Systemarchitektur, Kapitel „Sicherheitsbetrachtung“ (docs/architektur.html#k17)</t>
+          <t>Architektur, Kapitel 15 und 17; Funktion buildDemoRegistrations im EventContext; Auskunft des Betriebs vom 2026-08-17.
+Systemarchitektur, Kapitel „Deployment und Rollback“ (docs/architektur.html#k15)</t>
         </is>
       </c>
       <c r="E33" s="34" t="n"/>
-      <c r="F33" s="39" t="inlineStr">
-        <is>
-          <t>DEX</t>
+      <c r="F33" s="35" t="inlineStr">
+        <is>
+          <t>Zur Bewertung</t>
         </is>
       </c>
       <c r="G33" s="34" t="inlineStr">
         <is>
-          <t>Produktionsdaten werden nicht für Tests verwendet. Der Demo-Modus erzeugt seine Teilnehmerdaten synthetisch im Browser; es gibt keinen Export von Teilnehmerlisten in eine Testumgebung. Personenbezogene Daten verlassen die Produktiv-Site nicht.</t>
-        </is>
-      </c>
-      <c r="H33" s="34" t="inlineStr"/>
+          <t>Für die Anwendung erfüllt: Produktionsdaten werden nicht für Tests verwendet, der Demo-Modus erzeugt seine Teilnehmerdaten synthetisch im Browser, und es gibt keinen Export von Teilnehmerlisten in eine Testumgebung.</t>
+        </is>
+      </c>
+      <c r="H33" s="34" t="inlineStr">
+        <is>
+          <t>Abweichung auf der Flow-Seite, die die Anwendungs-Seite nicht aufwiegt: Die Flows liegen in der DEV-Umgebung und verarbeiten von dort personenbezogene Produktivdaten — Namen und E-Mail-Adressen der Teilnehmer stehen in jeder Bestätigungsmail, die dort erzeugt wird. Damit werden Produktivdaten in einer als Nicht-Produktion kategorisierten Umgebung verarbeitet. Nicht erfüllt, bis das Zielmodell greift (siehe GCM-07 bis GCM-11).</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="40" t="inlineStr">

--- a/docs/downloads/DEX-Requirements-kommentiert.xlsx
+++ b/docs/downloads/DEX-Requirements-kommentiert.xlsx
@@ -1117,7 +1117,7 @@
       </c>
       <c r="H6" s="34" t="inlineStr">
         <is>
-          <t>Befund mit bekanntem Abhilfeplan: Die Flow-Verbindungen laufen derzeit unter einem PERSÖNLICHEN Benutzerkonto, nicht unter einem Dienstkonto. Damit ist kein Vaulting im PAMS möglich — ein persönliches Konto gehört dort nicht hinein. Zwei Wirkungen: Die Anforderung ist nicht erfüllt, und der Betrieb der Plattform hängt an einer Person; scheidet sie aus, brechen alle Mails und Kalendereinträge ab. Geplant ist die Umstellung auf einen Service Principal. Damit wäre die Anforderung erfüllbar und GAC-02 sowie GAC-15 gleich mit. Bitte Zieltermin festhalten.</t>
+          <t>Befund mit bekanntem Abhilfeplan: Die Flow-Verbindungen laufen über ein Konto, das nach Auskunft des Betriebs als Dienstkonto geführt wird — dessen Adresse folgt aber dem Namensmuster für Personenkonten des Tenants (Initial und Nachname). Ein Assessor wird es deshalb als personalisiertes Konto einordnen, unabhängig von der internen Zweckbestimmung. Damit ist die Anforderung heute nicht belegbar: Ein auf eine Person lautendes Konto lässt sich nicht als Dienstkonto im PAMS führen, und es bringt die Mechanismen mit, die für Menschen gedacht sind — Postfach, interaktive Anmeldung, Mehrfaktor. Hinzu kommt das Betriebsrisiko: Verlässt die Person die Organisation, brechen Mails, Kalendereinträge und Nummernvergabe ab, ohne dass die Anwendung es merkt. Vorgesehen ist die Umstellung auf einen Service Principal als Teil des Zielmodells; damit lösen sich GAC-01, GAC-02 und GAC-15 gemeinsam. Der konkrete Kontoname liegt dem Review als Nachweis vor, steht aber bewusst nicht in der veröffentlichten Dokumentation. Bitte Zieltermin festhalten.</t>
         </is>
       </c>
     </row>
@@ -1157,7 +1157,7 @@
       </c>
       <c r="H7" s="34" t="inlineStr">
         <is>
-          <t>Derzeit ist die Verbindungs-Identität ein persönliches Konto (siehe GAC-01). Formal ist die Anforderung damit erfüllt — die Zugangsdaten liegen ausschliesslich bei ihrem Eigentümer —, aber aus dem falschen Grund: Es gibt keinen autorisierten Vertreter, weil es keine Delegation gibt. Mit dem geplanten Service Principal wird daraus eine bewusst verwaltete Berechtigung mit benennbaren Verantwortlichen.</t>
+          <t>Die Verbindungs-Identität ist ein personalisiert benanntes Konto (siehe GAC-01). Formal ist die Anforderung damit erfüllt — die Zugangsdaten liegen bei ihrem Eigentümer —, aber aus dem falschen Grund: Es gibt keinen autorisierten Vertreter, weil es keine Delegation gibt. Fällt der Eigentümer aus, gibt es niemanden, der eintreten darf. Mit dem geplanten Service Principal wird daraus eine verwaltete Berechtigung mit benennbaren Verantwortlichen und einer Freigabeliste, die man vorzeigen kann.</t>
         </is>
       </c>
     </row>
@@ -1484,7 +1484,7 @@
       </c>
       <c r="H16" s="34" t="inlineStr">
         <is>
-          <t>Heute nicht anwendbar, weil die Flows unter einem persönlichen Konto laufen (GAC-01) — und dem kann die interaktive Anmeldung nicht entzogen werden, es ist ja ein Mensch. Mit der Umstellung auf einen Service Principal löst sich die Anforderung von selbst: Ein Service Principal hat gar keine interaktive Anmeldung. Der Punkt ist also nicht separat zu bearbeiten, sondern erledigt sich mit GAC-01.</t>
+          <t>Heute nicht erfüllbar: Das Konto der Flow-Verbindungen ist ein Benutzerkonto mit Postfach (siehe GAC-01), und einem solchen lässt sich die interaktive Anmeldung nicht entziehen, ohne es funktionsunfähig zu machen. Mit der Umstellung auf einen Service Principal löst sich die Anforderung von selbst — ein Service Principal hat gar keine interaktive Anmeldung. Der Punkt ist also nicht separat zu bearbeiten.</t>
         </is>
       </c>
     </row>

--- a/docs/downloads/DEX-Requirements-kommentiert.xlsx
+++ b/docs/downloads/DEX-Requirements-kommentiert.xlsx
@@ -799,7 +799,7 @@
     <row r="3">
       <c r="A3" s="20" t="inlineStr">
         <is>
-          <t>Stand der Anwendung: v29.11.0</t>
+          <t>Stand der Anwendung: v29.12.0</t>
         </is>
       </c>
       <c r="B3" s="19" t="n"/>
@@ -1100,8 +1100,8 @@
       <c r="D6" s="34" t="inlineStr">
         <is>
           <t>NOTE: The implementation of this security requirement must be verified validated by the SSDLC assessor.
-Architektur, Kapitel 7 „Die sieben Flows“; Auskunft des Betriebs vom 2026-08-17.
-Systemarchitektur, Kapitel „Die sieben Flows“ (docs/architektur.html#k7)</t>
+Architektur, Kapitel 7 „Die acht Flows“; Auskunft des Betriebs vom 2026-08-17.
+Systemarchitektur, Kapitel „Die acht Flows“ (docs/architektur.html#k7)</t>
         </is>
       </c>
       <c r="E6" s="34" t="n"/>
@@ -1112,7 +1112,7 @@
       </c>
       <c r="G6" s="34" t="inlineStr">
         <is>
-          <t>DEX bringt keine eigenen privilegierten Konten mit. Im Umfang liegen zwei: die Websitesammlungs-Administratoren der SharePoint-Site (tenantverwaltet) und die Verbindungs-Identität der sieben Power-Automate-Flows, die auf den Event-Subsites Vollzugriff braucht.</t>
+          <t>DEX bringt keine eigenen privilegierten Konten mit. Im Umfang liegen zwei: die Websitesammlungs-Administratoren der SharePoint-Site (tenantverwaltet) und die Verbindungs-Identität der acht Power-Automate-Flows, die auf den Event-Subsites Vollzugriff braucht.</t>
         </is>
       </c>
       <c r="H6" s="34" t="inlineStr">
@@ -1141,7 +1141,7 @@
         <is>
           <t>NOTE: The implementation of this security requirement must be verified validated by the SSDLC assessor.
 Architektur, Kapitel 7; Auskunft des Betriebs vom 2026-08-17.
-Systemarchitektur, Kapitel „Die sieben Flows“ (docs/architektur.html#k7)</t>
+Systemarchitektur, Kapitel „Die acht Flows“ (docs/architektur.html#k7)</t>
         </is>
       </c>
       <c r="E7" s="34" t="n"/>
@@ -1468,7 +1468,7 @@
       <c r="D16" s="34" t="inlineStr">
         <is>
           <t>Architektur, Kapitel 7; Auskunft des Betriebs vom 2026-08-17.
-Systemarchitektur, Kapitel „Die sieben Flows“ (docs/architektur.html#k7)</t>
+Systemarchitektur, Kapitel „Die acht Flows“ (docs/architektur.html#k7)</t>
         </is>
       </c>
       <c r="E16" s="34" t="n"/>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="G28" s="34" t="inlineStr">
         <is>
-          <t>Es gibt zwei benannte Umgebungen für die Automatisierung, DEV und PROD. Die Kategorisierung beschreibt den Betrieb aber nicht: Die sieben Flows liegen vollständig in der DEV-Umgebung und laufen von dort produktiv gegen die Produktiv-Site. Sie sind fertig und werden nicht mehr weiterentwickelt — die DEV-Umgebung ist damit faktisch die Produktionsumgebung. Für die SPFx-Anwendung existiert gar keine zweite Umgebung; sie liegt allein auf der Produktiv-Site.</t>
+          <t>Es gibt zwei benannte Umgebungen für die Automatisierung, DEV und PROD. Die Kategorisierung beschreibt den Betrieb aber nicht: Die acht Flows liegen vollständig in der DEV-Umgebung und laufen von dort produktiv gegen die Produktiv-Site. Sie sind fertig und werden nicht mehr weiterentwickelt — die DEV-Umgebung ist damit faktisch die Produktionsumgebung. Für die SPFx-Anwendung existiert gar keine zweite Umgebung; sie liegt allein auf der Produktiv-Site.</t>
         </is>
       </c>
       <c r="H28" s="34" t="inlineStr">
